--- a/output/full_scan/batch_seq8_2026-08-07.xlsx
+++ b/output/full_scan/batch_seq8_2026-08-07.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2594,38 +2594,38 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7689</v>
+        <v>6969</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>415.4019761415498</v>
+        <v>423.638083606199</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>164</v>
+        <v>35.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G41" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>18.73748763550472</v>
+        <v>62.41035460469017</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>30.70526298413127</v>
+        <v>21.09527525233668</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.740197614154974</v>
+        <v>0.4837628820095946</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-2.875998878588732</v>
+        <v>0.3818431280931222</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6937</v>
+        <v>7689</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>397.5425636849615</v>
+        <v>415.4019761415498</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>262.5</v>
+        <v>164</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>48.5727170661686</v>
+        <v>18.73748763550472</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>9.731788517539764</v>
+        <v>30.70526298413127</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5308716521365752</v>
+        <v>1.740197614154974</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.2132274140603067</v>
+        <v>-2.875998878588732</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6865</v>
+        <v>7610</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>394.5617744346445</v>
+        <v>413.0068432407118</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>24.7</v>
+        <v>1850</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.02862981909401</v>
+        <v>52.51373820413838</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>8.442759262780113</v>
+        <v>29.06097001059134</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.1262534829904129</v>
+        <v>0.5613620219458169</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.7584357978828491</v>
+        <v>10.33466875159775</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7749</v>
+        <v>6937</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>386.8430241771023</v>
+        <v>397.5425636849615</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>347.5</v>
+        <v>262.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>40.62237260798368</v>
+        <v>48.5727170661686</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>34.46681585429653</v>
+        <v>9.731788517539764</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3406417745204819</v>
+        <v>0.5308716521365752</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>2</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>3.409192101332334</v>
+        <v>-0.2132274140603067</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7842</v>
+        <v>6865</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>384.8347836246289</v>
+        <v>394.5617744346445</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>83.3</v>
+        <v>24.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.22047911501777</v>
+        <v>51.02862981909401</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10.4106950791311</v>
+        <v>8.442759262780113</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.17395352225697</v>
+        <v>0.1262534829904129</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,51 +2849,51 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.299258903649612</v>
+        <v>0.7584357978828491</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7717</v>
+        <v>7749</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>384.7306314350374</v>
+        <v>386.8430241771023</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>419</v>
+        <v>347.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G46" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46.38288989982885</v>
+        <v>40.62237260798368</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25.28436227320066</v>
+        <v>34.46681585429653</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5109982563026917</v>
+        <v>0.3406417745204819</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,51 +2902,51 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>7.019289527666754</v>
+        <v>3.409192101332334</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7722</v>
+        <v>7842</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>375.1326618442034</v>
+        <v>384.8347836246289</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>274.5</v>
+        <v>83.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G47" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>40.44621216001455</v>
+        <v>48.22047911501777</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>24.44646009489701</v>
+        <v>10.4106950791311</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4441587542674199</v>
+        <v>1.17395352225697</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,51 +2955,51 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-2.272954706217749</v>
+        <v>0.299258903649612</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7827</v>
+        <v>7717</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>374.0555023699349</v>
+        <v>384.7306314350374</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>156.5</v>
+        <v>419</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.42481054785771</v>
+        <v>46.38288989982885</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.41142288422823</v>
+        <v>25.28436227320066</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.085360816859852</v>
+        <v>0.5109982563026917</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.7805579633272415</v>
+        <v>7.019289527666754</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6921</v>
+        <v>7722</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>373.3963865196977</v>
+        <v>375.1326618442034</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>64.5</v>
+        <v>274.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>49.78432109287554</v>
+        <v>40.44621216001455</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>29.29914381340418</v>
+        <v>24.44646009489701</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.631828208509614</v>
+        <v>0.4441587542674199</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.390409359102891</v>
+        <v>-2.272954706217749</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6862</v>
+        <v>7827</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>372.9691232384678</v>
+        <v>374.0555023699349</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>144</v>
+        <v>156.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>43.9415030637004</v>
+        <v>52.42481054785771</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>24.63591404154948</v>
+        <v>16.41142288422823</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3998352533486989</v>
+        <v>1.085360816859852</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,48 +3114,48 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.534706510089434</v>
+        <v>0.7805579633272415</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7714</v>
+        <v>6921</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>371.1885264770223</v>
+        <v>373.3963865196977</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>153</v>
+        <v>64.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G51" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.71520067873226</v>
+        <v>49.78432109287554</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>23.22469020654714</v>
+        <v>29.29914381340418</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.2108877449780835</v>
+        <v>1.631828208509614</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,51 +3167,51 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-2.480479363225541</v>
+        <v>0.390409359102891</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8040</v>
+        <v>6862</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>365.1839584331537</v>
+        <v>372.9691232384678</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>42.77308509147537</v>
+        <v>43.9415030637004</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>27.19778624615104</v>
+        <v>24.63591404154948</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7060566524144869</v>
+        <v>0.3998352533486989</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,48 +3220,48 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.9702885321549548</v>
+        <v>1.534706510089434</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6869</v>
+        <v>7714</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>364.2068916323527</v>
+        <v>371.1885264770223</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>67.8</v>
+        <v>153</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G53" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.47458023312749</v>
+        <v>48.71520067873226</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.45075472027677</v>
+        <v>23.22469020654714</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6629391551698346</v>
+        <v>0.2108877449780835</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.4788980651892736</v>
+        <v>-2.480479363225541</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8043</v>
+        <v>8040</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>350.271298948509</v>
+        <v>365.1839584331537</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>38.97970667229743</v>
+        <v>42.77308509147537</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>24.33957687805437</v>
+        <v>27.19778624615104</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4912240218088556</v>
+        <v>0.7060566524144869</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.09198966637611861</v>
+        <v>0.9702885321549548</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6901</v>
+        <v>6869</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>348.1060177888945</v>
+        <v>364.2068916323527</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>17.5</v>
+        <v>67.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.16606810716981</v>
+        <v>44.47458023312749</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>22.01328035096958</v>
+        <v>21.45075472027677</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3236179507382224</v>
+        <v>0.6629391551698346</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,51 +3379,51 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0931643251274954</v>
+        <v>0.4788980651892736</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7721</v>
+        <v>8043</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>347.3518143410534</v>
+        <v>350.271298948509</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>61.4</v>
+        <v>126</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G56" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>42.80190522534922</v>
+        <v>38.97970667229743</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>26.43506194858149</v>
+        <v>24.33957687805437</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4118388078209144</v>
+        <v>0.4912240218088556</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,48 +3432,48 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.3564675810391433</v>
+        <v>0.09198966637611861</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7747</v>
+        <v>6901</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>324.825860326264</v>
+        <v>348.1060177888945</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G57" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>38.75054631478917</v>
+        <v>51.16606810716981</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.40651020198785</v>
+        <v>22.01328035096958</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0</v>
+        <v>0.3236179507382224</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,51 +3485,51 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-5.780788517240538</v>
+        <v>-0.0931643251274954</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7839</v>
+        <v>7721</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>312.5471046389306</v>
+        <v>347.3518143410534</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>45</v>
+        <v>61.4</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G58" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.5081617677332</v>
+        <v>42.80190522534922</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.91791775787253</v>
+        <v>26.43506194858149</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.2637009104273932</v>
+        <v>0.4118388078209144</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,48 +3538,48 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.3234148430164388</v>
+        <v>0.3564675810391433</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7732</v>
+        <v>7747</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>311.530229110045</v>
+        <v>324.825860326264</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>35.6</v>
+        <v>0</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.66765405099371</v>
+        <v>38.75054631478917</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4.248959022690053</v>
+        <v>18.40651020198785</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3744799409819613</v>
+        <v>0</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1033083818709986</v>
+        <v>-5.780788517240538</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7738</v>
+        <v>7839</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>310.4618104241727</v>
+        <v>312.5471046389306</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>166.5</v>
+        <v>45</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>47.52107331396743</v>
+        <v>46.5081617677332</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>28.81477122546152</v>
+        <v>11.91791775787253</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.1972620355753036</v>
+        <v>0.2637009104273932</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0938491583163555</v>
+        <v>0.3234148430164388</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7780</v>
+        <v>7732</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>308.0065588751249</v>
+        <v>311.530229110045</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>16.7</v>
+        <v>35.6</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>34.41287161693619</v>
+        <v>51.66765405099371</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>34.68928921878002</v>
+        <v>4.248959022690053</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7038863364735299</v>
+        <v>0.3744799409819613</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0266161521743326</v>
+        <v>-0.1033083818709986</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6922</v>
+        <v>7738</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>302.9501776219397</v>
+        <v>310.4618104241727</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>185.5</v>
+        <v>166.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>53.28923694452549</v>
+        <v>47.52107331396743</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14.87130591333892</v>
+        <v>28.81477122546152</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.89237055893919</v>
+        <v>0.1972620355753036</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>1.713616420890878</v>
+        <v>0.0938491583163555</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6965</v>
+        <v>7780</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>297.9205350100312</v>
+        <v>308.0065588751249</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>76.7</v>
+        <v>16.7</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.10320458106478</v>
+        <v>34.41287161693619</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>32.0436375947092</v>
+        <v>34.68928921878002</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8299642077602267</v>
+        <v>0.7038863364735299</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.1930710063605148</v>
+        <v>-0.0266161521743326</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7734</v>
+        <v>8033</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>297.8388882374359</v>
+        <v>303.0640284302916</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>3375</v>
+        <v>185</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>53.53687433448056</v>
+        <v>50.06257375223301</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>11.09058649266335</v>
+        <v>22.64597294140758</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.405741739824007</v>
+        <v>0.0811966792782501</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>32.13349162048476</v>
+        <v>-2.395657144054909</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6859</v>
+        <v>6922</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>295.4074632116221</v>
+        <v>302.9501776219397</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>99.2</v>
+        <v>185.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>35.08562392318012</v>
+        <v>53.28923694452549</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>28.30782300460556</v>
+        <v>14.87130591333892</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.137029421138339</v>
+        <v>0.89237055893919</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,48 +3909,48 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.8534090295689269</v>
+        <v>1.713616420890878</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6894</v>
+        <v>6965</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>293.0481498613086</v>
+        <v>297.9205350100312</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>347</v>
+        <v>76.7</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G66" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.28739555374353</v>
+        <v>43.10320458106478</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>16.86182468553925</v>
+        <v>32.0436375947092</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4764884437917175</v>
+        <v>0.8299642077602267</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>4.529202792172315</v>
+        <v>-0.1930710063605148</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7712</v>
+        <v>7734</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>287.9765020527436</v>
+        <v>297.8388882374359</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>141</v>
+        <v>3375</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.64901860928627</v>
+        <v>53.53687433448056</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>26.11036198581344</v>
+        <v>11.09058649266335</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6248779132994415</v>
+        <v>0.405741739824007</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>1.141456359915708</v>
+        <v>32.13349162048476</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6870</v>
+        <v>6859</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>285.7888087562145</v>
+        <v>295.4074632116221</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>256</v>
+        <v>99.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.80966121412368</v>
+        <v>35.08562392318012</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17.30762223485459</v>
+        <v>28.30782300460556</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3723772655272185</v>
+        <v>1.137029421138339</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,51 +4068,51 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.951648213819742</v>
+        <v>0.8534090295689269</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6854</v>
+        <v>7828</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>282.2142162337257</v>
+        <v>295.1815259704255</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>97</v>
+        <v>1710</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G69" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>40.35159221765482</v>
+        <v>49.65180481616096</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>41.93338972305743</v>
+        <v>16.75911180062651</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4024576072894771</v>
+        <v>0.2532375767337725</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>1.221249827513261</v>
+        <v>10.6211314258978</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7556</v>
+        <v>6894</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>279.7293427611564</v>
+        <v>293.0481498613086</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>223</v>
+        <v>347</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>44.06656296431096</v>
+        <v>53.28739555374353</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>34.24977732028549</v>
+        <v>16.86182468553925</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.395639246020702</v>
+        <v>0.4764884437917175</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,51 +4174,51 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>2.814807323035714</v>
+        <v>4.529202792172315</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6936</v>
+        <v>7712</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>271.6450485574047</v>
+        <v>287.9765020527436</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>31.9</v>
+        <v>141</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G71" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>44.53982674181945</v>
+        <v>44.64901860928627</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.96379191578062</v>
+        <v>26.11036198581344</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.045315299080974</v>
+        <v>0.6248779132994415</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,51 +4227,51 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0483370542407218</v>
+        <v>1.141456359915708</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7631</v>
+        <v>6870</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>271.4589128659065</v>
+        <v>285.7888087562145</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>132</v>
+        <v>256</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G72" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>43.19870121810403</v>
+        <v>46.80966121412368</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11.34447545848354</v>
+        <v>17.30762223485459</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3808430345660598</v>
+        <v>0.3723772655272185</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-1.025822183904567</v>
+        <v>-0.951648213819742</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6902</v>
+        <v>6854</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>271.0786166865307</v>
+        <v>282.2142162337257</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>123.5</v>
+        <v>97</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>48.71648202422593</v>
+        <v>40.35159221765482</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>18.38353078346206</v>
+        <v>41.93338972305743</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.053638944374307</v>
+        <v>0.4024576072894771</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.4630352289461998</v>
+        <v>1.221249827513261</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7792</v>
+        <v>7556</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>264.9279129882492</v>
+        <v>279.7293427611564</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.89447984753787</v>
+        <v>44.06656296431096</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>32.72875235196314</v>
+        <v>34.24977732028549</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.276866666741558</v>
+        <v>0.395639246020702</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,51 +4386,51 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>2.730818506020874</v>
+        <v>2.814807323035714</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7772</v>
+        <v>6936</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>257.5493760562164</v>
+        <v>271.6450485574047</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>91</v>
+        <v>31.9</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G75" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>36.3513475737228</v>
+        <v>44.53982674181945</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>29.42630057770722</v>
+        <v>13.96379191578062</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4473105006518404</v>
+        <v>1.045315299080974</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,51 +4439,51 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>1.872755587944797</v>
+        <v>0.0483370542407218</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6910</v>
+        <v>7631</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>255.1046458582024</v>
+        <v>271.4589128659065</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>24.7</v>
+        <v>132</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G76" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>41.10665780031577</v>
+        <v>43.19870121810403</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>24.67383783569855</v>
+        <v>11.34447545848354</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.1939054666562062</v>
+        <v>0.3808430345660598</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.09818704397196951</v>
+        <v>-1.025822183904567</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6909</v>
+        <v>6902</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>251.8321340626823</v>
+        <v>271.0786166865307</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>40.85</v>
+        <v>123.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>38.4685202963694</v>
+        <v>48.71648202422593</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>31.18780224350741</v>
+        <v>18.38353078346206</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4106463103333529</v>
+        <v>1.053638944374307</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,51 +4545,51 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.09810257143476959</v>
+        <v>0.4630352289461998</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7821</v>
+        <v>7792</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>247.1077775620772</v>
+        <v>264.9279129882492</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>40.15</v>
+        <v>207</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G78" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>41.5928963186985</v>
+        <v>43.89447984753787</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19.50379686319956</v>
+        <v>32.72875235196314</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.333835816553983</v>
+        <v>1.276866666741558</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,51 +4598,51 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.1003250803530163</v>
+        <v>2.730818506020874</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6951</v>
+        <v>7772</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>244.1807003623512</v>
+        <v>257.5493760562164</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>70.8</v>
+        <v>91</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G79" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>32.61866471127641</v>
+        <v>36.3513475737228</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>39.01890426718996</v>
+        <v>29.42630057770722</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.817356115453183</v>
+        <v>0.4473105006518404</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.1416846773950673</v>
+        <v>1.872755587944797</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7810</v>
+        <v>6910</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>241.6988700982185</v>
+        <v>255.1046458582024</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>200.5</v>
+        <v>24.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>55.22596052865597</v>
+        <v>41.10665780031577</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.79807987046698</v>
+        <v>24.67383783569855</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6670290850344907</v>
+        <v>0.1939054666562062</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.751360392578674</v>
+        <v>0.09818704397196951</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6919</v>
+        <v>6909</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>240.5567833992043</v>
+        <v>251.8321340626823</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>107.5</v>
+        <v>40.85</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>54.66951606044875</v>
+        <v>38.4685202963694</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16.0562260608197</v>
+        <v>31.18780224350741</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5649563309131493</v>
+        <v>0.4106463103333529</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.3747471828297443</v>
+        <v>0.09810257143476959</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7818</v>
+        <v>7821</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>234.4502917609148</v>
+        <v>247.1077775620772</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>62</v>
+        <v>40.15</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>26.74928516470192</v>
+        <v>41.5928963186985</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>33.95477218863164</v>
+        <v>19.50379686319956</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5534880286379524</v>
+        <v>1.333835816553983</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.6405295582088155</v>
+        <v>0.1003250803530163</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6931</v>
+        <v>6951</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>233.8561402064315</v>
+        <v>244.1807003623512</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>37.3</v>
+        <v>70.8</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>36.7411664961999</v>
+        <v>32.61866471127641</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>20.90613059957517</v>
+        <v>39.01890426718996</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.105887083605101</v>
+        <v>0.817356115453183</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0638265245614783</v>
+        <v>0.1416846773950673</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7805</v>
+        <v>7810</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>232.5766935946583</v>
+        <v>241.6988700982185</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>644</v>
+        <v>200.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>55.42373857836286</v>
+        <v>55.22596052865597</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>29.35349071619979</v>
+        <v>14.79807987046698</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.7591293619154824</v>
+        <v>0.6670290850344907</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>8.224958217816368</v>
+        <v>1.751360392578674</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7803</v>
+        <v>6919</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>230.8609300269833</v>
+        <v>240.5567833992043</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>20.7</v>
+        <v>107.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45.22657793107582</v>
+        <v>54.66951606044875</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>22.27462823045221</v>
+        <v>16.0562260608197</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6082988354369759</v>
+        <v>0.5649563309131493</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,51 +4969,51 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0284172455115601</v>
+        <v>0.3747471828297443</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8032</v>
+        <v>7818</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>229.8077323458505</v>
+        <v>234.4502917609148</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>36.1</v>
+        <v>62</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G86" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>41.29186479075677</v>
+        <v>26.74928516470192</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>33.05136598529093</v>
+        <v>33.95477218863164</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.8018481969914028</v>
+        <v>0.5534880286379524</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.3033802294775924</v>
+        <v>-0.6405295582088155</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5032,21 +5032,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6885</v>
+        <v>6931</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>228.8954504155464</v>
+        <v>233.8561402064315</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>21</v>
+        <v>37.3</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>47.24804973722386</v>
+        <v>36.7411664961999</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11.06336599036787</v>
+        <v>20.90613059957517</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5991466593160778</v>
+        <v>1.105887083605101</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.058168582915561</v>
+        <v>-0.0638265245614783</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6925</v>
+        <v>7805</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>227.8978791699026</v>
+        <v>232.5766935946583</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>53.2</v>
+        <v>644</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>42.43745533424418</v>
+        <v>55.42373857836286</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17.17448062676502</v>
+        <v>29.35349071619979</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3712306575340342</v>
+        <v>0.7591293619154824</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.3235024481092612</v>
+        <v>8.224958217816368</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>rsi_strong, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6908</v>
+        <v>7803</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>226.933901996451</v>
+        <v>230.8609300269833</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>33.6</v>
+        <v>20.7</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>36.96443944799273</v>
+        <v>45.22657793107582</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>29.85695592456684</v>
+        <v>22.27462823045221</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.2583616093068347</v>
+        <v>0.6082988354369759</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0924562181708974</v>
+        <v>0.0284172455115601</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8024</v>
+        <v>8032</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>225.1512999594622</v>
+        <v>229.8077323458505</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>14.4</v>
+        <v>36.1</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.44481526739442</v>
+        <v>41.29186479075677</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>19.82928336353151</v>
+        <v>33.05136598529093</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.2003953600339532</v>
+        <v>0.8018481969914028</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.1473794124267915</v>
+        <v>0.3033802294775924</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6890</v>
+        <v>6885</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>223.967489973851</v>
+        <v>228.8954504155464</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>170.5</v>
+        <v>21</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.89509704000442</v>
+        <v>47.24804973722386</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>15.5737307516865</v>
+        <v>11.06336599036787</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.4245897430055731</v>
+        <v>0.5991466593160778</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,51 +5287,51 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.7811728387929904</v>
+        <v>0.058168582915561</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6923</v>
+        <v>6925</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>223.6501922809645</v>
+        <v>227.8978791699025</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>53.2</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G92" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>43.9787265541524</v>
+        <v>42.43745533424418</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.43000186237238</v>
+        <v>17.17448062676502</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5047003484879381</v>
+        <v>0.3712306575340342</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.3384561481432115</v>
+        <v>0.3235024481092612</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7740</v>
+        <v>6908</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>223.2402188142813</v>
+        <v>226.933901996451</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>155</v>
+        <v>33.6</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.6760347986142</v>
+        <v>36.96443944799273</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>14.82462685170163</v>
+        <v>29.85695592456684</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.6829241170152272</v>
+        <v>0.2583616093068347</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,51 +5393,51 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.9849376973289208</v>
+        <v>-0.0924562181708974</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6906</v>
+        <v>8024</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>219.4513576685233</v>
+        <v>225.1512999594622</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>73.7</v>
+        <v>14.4</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G94" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.44216580112147</v>
+        <v>46.44481526739442</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>31.32707246123671</v>
+        <v>19.82928336353151</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.496536451296112</v>
+        <v>0.2003953600339532</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,48 +5446,48 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.7136412202042468</v>
+        <v>-0.1473794124267915</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7820</v>
+        <v>6890</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>215.0245046853783</v>
+        <v>223.967489973851</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>110</v>
+        <v>170.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G95" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>51.79570622231322</v>
+        <v>41.89509704000442</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>19.97065530317861</v>
+        <v>15.5737307516865</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.097000289361155</v>
+        <v>0.4245897430055731</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,51 +5499,51 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.586937427674215</v>
+        <v>0.7811728387929904</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6899</v>
+        <v>6923</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>213.824375549267</v>
+        <v>223.6501922809645</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>50.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G96" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>38.55263738138352</v>
+        <v>43.9787265541524</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>24.56818286411022</v>
+        <v>12.43000186237238</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4351331754823531</v>
+        <v>0.5047003484879381</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,48 +5552,48 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.3254518246630173</v>
+        <v>-0.3384561481432115</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6983</v>
+        <v>7740</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>211.1233596951961</v>
+        <v>223.2402188142813</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>298.5</v>
+        <v>155</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G97" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>37.57960313881382</v>
+        <v>52.6760347986142</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.38823247671658</v>
+        <v>14.82462685170163</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.7271440842360301</v>
+        <v>0.6829241170152272</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0882673471453046</v>
+        <v>0.9849376973289208</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6916</v>
+        <v>6906</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>209.1679969370884</v>
+        <v>219.4513576685233</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>18.2</v>
+        <v>73.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.52424155301461</v>
+        <v>46.44216580112147</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.47409330213428</v>
+        <v>31.32707246123671</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3138018478653101</v>
+        <v>0.496536451296112</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,48 +5658,48 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0949561647126375</v>
+        <v>0.7136412202042468</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6887</v>
+        <v>7820</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>208.239612121349</v>
+        <v>215.0245046853783</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>36.45</v>
+        <v>110</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G99" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>49.23604537412398</v>
+        <v>51.79570622231322</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.64856654411664</v>
+        <v>19.97065530317861</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.1689950929161704</v>
+        <v>1.097000289361155</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1468550451321325</v>
+        <v>0.586937427674215</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6877</v>
+        <v>6899</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>205.2976229464678</v>
+        <v>213.824375549267</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>122</v>
+        <v>50.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>47.47649500168421</v>
+        <v>38.55263738138352</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>19.48634345709554</v>
+        <v>24.56818286411022</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5166857788479765</v>
+        <v>0.4351331754823531</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,51 +5764,51 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>1.094858351827499</v>
+        <v>0.3254518246630173</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7791</v>
+        <v>6983</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>204.8688934209964</v>
+        <v>211.1233596951961</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>59.6</v>
+        <v>298.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G101" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>31.91687074674272</v>
+        <v>37.57960313881382</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>24.40248761024355</v>
+        <v>12.38823247671658</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.8176014851955725</v>
+        <v>0.7271440842360301</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,51 +5817,51 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.2023818896016793</v>
+        <v>-0.0882673471453046</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8034</v>
+        <v>6916</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>198.9742786620891</v>
+        <v>209.1679969370884</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>19.1</v>
+        <v>18.2</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G102" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.79083768553031</v>
+        <v>42.52424155301461</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>36.34762480771393</v>
+        <v>15.47409330213428</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.210284665563166</v>
+        <v>0.3138018478653101</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,51 +5870,51 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1415675708681506</v>
+        <v>-0.0949561647126375</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6967</v>
+        <v>6887</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>198.0658713397563</v>
+        <v>208.239612121349</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>36.45</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G103" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>42.05488668098848</v>
+        <v>49.23604537412398</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.48564300837863</v>
+        <v>16.64856654411664</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.29791339145348</v>
+        <v>0.1689950929161704</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,51 +5923,51 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.4399023057534516</v>
+        <v>-0.1468550451321325</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7786</v>
+        <v>6877</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>197.2187608605282</v>
+        <v>205.2976229464677</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>123.5</v>
+        <v>122</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G104" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>45.19232319497593</v>
+        <v>47.47649500168421</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.56487898511784</v>
+        <v>19.48634345709554</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.5603921467805</v>
+        <v>0.5166857788479765</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,51 +5976,51 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.6396189810699529</v>
+        <v>1.094858351827499</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7402</v>
+        <v>7791</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>196.3643775714775</v>
+        <v>204.8688934209964</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>103.5</v>
+        <v>59.6</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G105" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>44.60608697446216</v>
+        <v>31.91687074674272</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>21.0513208102589</v>
+        <v>24.40248761024355</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.1358645576129739</v>
+        <v>0.8176014851955725</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,51 +6029,51 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-1.021158465633641</v>
+        <v>-0.2023818896016793</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8011</v>
+        <v>8034</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>187.7617026107613</v>
+        <v>198.9742786620891</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>16.4</v>
+        <v>19.1</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G106" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45.03458317556558</v>
+        <v>39.79083768553031</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>28.81528663188712</v>
+        <v>36.34762480771393</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.327607368034113</v>
+        <v>1.210284665563166</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.08867668872351531</v>
+        <v>0.1415675708681506</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6895</v>
+        <v>6967</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>175.1691238016852</v>
+        <v>198.0658713397563</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>115</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>31.78356772998193</v>
+        <v>42.05488668098848</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>27.75179704765827</v>
+        <v>16.48564300837863</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5016081157533344</v>
+        <v>0.29791339145348</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.7495057346760703</v>
+        <v>-0.4399023057534516</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7799</v>
+        <v>7786</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>170.8819322053963</v>
+        <v>197.2187608605282</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>357</v>
+        <v>123.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.31395893878496</v>
+        <v>45.19232319497593</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>22.01531886023359</v>
+        <v>13.56487898511784</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3332931175341063</v>
+        <v>1.5603921467805</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,48 +6188,48 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-5.624303624878074</v>
+        <v>-0.6396189810699529</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>7760</v>
+        <v>7402</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>151.0597103683878</v>
+        <v>196.3643775714775</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>33.65</v>
+        <v>103.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G109" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>45.58547412115715</v>
+        <v>44.60608697446216</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>16.20842471718117</v>
+        <v>21.0513208102589</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.25444515219362</v>
+        <v>0.1358645576129739</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,48 +6241,48 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.1559135734526114</v>
+        <v>-1.021158465633641</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7703</v>
+        <v>8011</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>150.6783597636592</v>
+        <v>187.7617026107613</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>178</v>
+        <v>16.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G110" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>47.43354078849018</v>
+        <v>45.03458317556558</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>21.90033877531455</v>
+        <v>28.81528663188712</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4200539505536718</v>
+        <v>0.327607368034113</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,48 +6294,48 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>1.097014568764616</v>
+        <v>0.08867668872351531</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6934</v>
+        <v>6895</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>150.0764426246642</v>
+        <v>175.1691238016852</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>73.2</v>
+        <v>115</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G111" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45.53213623946513</v>
+        <v>31.78356772998193</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.41410393637931</v>
+        <v>27.75179704765827</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.7206101866548456</v>
+        <v>0.5016081157533344</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,48 +6347,48 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.7202095716215043</v>
+        <v>0.7495057346760703</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6953</v>
+        <v>7799</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>146.5905564944593</v>
+        <v>170.8819322053963</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>215.5</v>
+        <v>357</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G112" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>47.58706680238474</v>
+        <v>42.31395893878496</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>10.30121362249821</v>
+        <v>22.01531886023359</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5550936567711645</v>
+        <v>0.3332931175341063</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,48 +6400,48 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>1.063895530284271</v>
+        <v>-5.624303624878074</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8038</v>
+        <v>7760</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>141.3537880369037</v>
+        <v>151.0597103683878</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>32.1</v>
+        <v>33.65</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G113" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>34.71114109161809</v>
+        <v>45.58547412115715</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>20.87170895975031</v>
+        <v>16.20842471718117</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3521625197158707</v>
+        <v>1.25444515219362</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,48 +6453,48 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1933376689466186</v>
+        <v>-0.1559135734526114</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>7736</v>
+        <v>7703</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>138.446179188635</v>
+        <v>150.6783597636592</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>178</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G114" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.9698179417452</v>
+        <v>47.43354078849018</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20.59661214316129</v>
+        <v>21.90033877531455</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4665610529908192</v>
+        <v>0.4200539505536718</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0258222664956115</v>
+        <v>1.097014568764616</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>7765</v>
+        <v>6934</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>133.666212618466</v>
+        <v>150.0764426246642</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>222</v>
+        <v>73.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>43.13195316986652</v>
+        <v>45.53213623946513</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>11.38254563211494</v>
+        <v>16.41410393637931</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.6952033851251688</v>
+        <v>0.7206101866548456</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.1535372326994593</v>
+        <v>-0.7202095716215043</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,41 +6569,41 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6873</v>
+        <v>6953</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>127.7479027949524</v>
+        <v>146.5905564944593</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>215.5</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G116" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>41.25663994668744</v>
+        <v>47.58706680238474</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.18081025122267</v>
+        <v>10.30121362249821</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5489370055245011</v>
+        <v>0.5550936567711645</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.602178513741122</v>
+        <v>1.063895530284271</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7728</v>
+        <v>8038</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>123.7068420530027</v>
+        <v>141.3537880369037</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>598</v>
+        <v>32.1</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>45.42561346277238</v>
+        <v>34.71114109161809</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>18.43818714295942</v>
+        <v>20.87170895975031</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.3281604770382965</v>
+        <v>0.3521625197158707</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>4.894617429925308</v>
+        <v>-0.1933376689466186</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6918</v>
+        <v>7736</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>118.9023237125114</v>
+        <v>138.446179188635</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>45.40902772267502</v>
+        <v>42.9698179417452</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13.97168991712265</v>
+        <v>20.59661214316129</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5275258534829675</v>
+        <v>0.4665610529908192</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,48 +6718,48 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0385634279532749</v>
+        <v>0.0258222664956115</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7753</v>
+        <v>7765</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>115.7862294079111</v>
+        <v>133.666212618466</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>37.6</v>
+        <v>222</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G119" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>40.23718175500854</v>
+        <v>43.13195316986652</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.7531680593821</v>
+        <v>11.38254563211494</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.102919349629317</v>
+        <v>0.6952033851251688</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.1175421427462724</v>
+        <v>0.1535372326994593</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,41 +6781,41 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6971</v>
+        <v>6873</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>108.207882318062</v>
+        <v>127.7479027949524</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>25.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G120" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>31.60088929515831</v>
+        <v>41.25663994668744</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>16.86190829986841</v>
+        <v>17.18081025122267</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5984223487872318</v>
+        <v>0.5489370055245011</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.1077611937501288</v>
+        <v>-0.602178513741122</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,38 +6834,38 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6988</v>
+        <v>7728</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>107.8289891549108</v>
+        <v>123.7068420530027</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>12.65</v>
+        <v>598</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G121" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>50.79930888943829</v>
+        <v>45.42561346277238</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>11.42872336267003</v>
+        <v>18.43818714295942</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.311064896073524</v>
+        <v>0.3281604770382965</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,48 +6877,48 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.1919658894037743</v>
+        <v>4.894617429925308</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6997</v>
+        <v>6918</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>100.601582356792</v>
+        <v>118.9023237125114</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G122" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>52.72153442961174</v>
+        <v>45.40902772267502</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>11.46851912838477</v>
+        <v>13.97168991712265</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.6982651461925093</v>
+        <v>0.5275258534829675</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,48 +6930,48 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>4.340924893913955</v>
+        <v>-0.0385634279532749</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6928</v>
+        <v>7753</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>81.05087844246094</v>
+        <v>115.7862294079111</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>48.4</v>
+        <v>37.6</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G123" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>45.78172892031582</v>
+        <v>40.23718175500854</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>18.88930379964664</v>
+        <v>13.7531680593821</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.181447058689112</v>
+        <v>1.102919349629317</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.4739124825080693</v>
+        <v>-0.1175421427462724</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7770</v>
+        <v>6971</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>66.64931119895665</v>
+        <v>108.207882318062</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>39.95</v>
+        <v>25.5</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>52.38271358395907</v>
+        <v>31.60088929515831</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13.34652773696779</v>
+        <v>16.86190829986841</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.141983746039819</v>
+        <v>0.5984223487872318</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,62 +7036,274 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.2897863294151048</v>
+        <v>-0.1077611937501288</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
+        <v>6988</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>威力暘-創</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>107.8289891549108</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>50.79930888943829</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>11.42872336267003</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>1.311064896073524</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.1919658894037743</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>6997</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>博弘</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>100.601582356792</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>52.72153442961174</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>11.46851912838477</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.6982651461925093</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>4.340924893913955</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>6928</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>攸泰科技</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>81.05087844246094</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>45.78172892031582</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>18.88930379964664</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.181447058689112</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.4739124825080693</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>7770</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>君曜</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>66.64931119895665</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>52.38271358395907</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>13.34652773696779</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.141983746039819</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>-0.2897863294151048</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
         <v>7823</v>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>奧義賽博-KY創</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
         <v>58.69150387738266</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E129" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
         <v>55.90183596543188</v>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="I129" s="2" t="n">
         <v>18.9229164701944</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J129" s="2" t="n">
         <v>0.4946995249037921</v>
       </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
         <v>0.4549050763267028</v>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>rsi_strong, market_above_ma60</t>
         </is>
